--- a/resources/data-imports/Monsters/weekly-monsters-delusional-memories.xlsx
+++ b/resources/data-imports/Monsters/weekly-monsters-delusional-memories.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -407,34 +407,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -580,7 +580,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.71"/>
@@ -840,7 +840,7 @@
         <v>0.04196742363147</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>1945259213.23494</v>
+        <v>4000000</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>0.0496372640720866</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>2215239016.07692</v>
+        <v>4931609</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0.0587088215421089</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>2522688937.78361</v>
+        <v>6080192</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
         <v>0.0694382696406801</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>2872809403.69409</v>
+        <v>7496283</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>0.0821285994854019</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>3271522598.89962</v>
+        <v>9242185</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1510,7 +1510,7 @@
         <v>0.0971381759415555</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>3725572640.26927</v>
+        <v>11394711</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         <v>0.114890857562106</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>4242639651.21054</v>
+        <v>14048565</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.135887966017584</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>4831469668.70654</v>
+        <v>17320508</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>0.16072244302306</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>5502022579.96878</v>
+        <v>21354494</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0.190095594542625</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>6265640591.01104</v>
+        <v>26328005</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
         <v>0.224836895114452</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>7135240076.74063</v>
+        <v>32459858</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>0.265927411554884</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>8125530057.65536</v>
+        <v>40019834</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
         <v>0.31452750750842</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>9253260998.61527</v>
+        <v>49340545</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>0.372009611198136</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>10537508138.0477</v>
+        <v>60832072</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>0.439996971711873</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>11999994140.0159</v>
+        <v>75000001</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>0</v>
